--- a/survey_templates/037_join_adventuring_party_survey--survey_templates.xlsx
+++ b/survey_templates/037_join_adventuring_party_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Player Details</t>
+          <t>Player Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>party_preferences</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Party Preferences</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>adventure_settings</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adventure Settings</t>
+          <t>Adventure Experience</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>party_preferences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Party Preferences</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>adventure_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Adventure Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>adventure_type</t>
+          <t>difficulty_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adventure Type</t>
+          <t>Difficulty Level</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>difficulty_level</t>
+          <t>party_size</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Difficulty Level</t>
+          <t>Party Size</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>character_class</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Character Class</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>character_class</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Character Class</t>
+          <t>Role in Party</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>adventure_settings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Adventure Settings</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>experience_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Experience Points</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>adventure_length_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Adventure Length 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,246 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>party_size</t>
+          <t>player_name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Party Size</t>
+          <t>Player Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>adventure_length</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Adventure Length</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>adventure_type</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Adventure Type</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>difficulty_level</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Difficulty Level</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>player_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Player Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>character_class</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Character Class</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>character_class</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Character Class</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>experience</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,10 +845,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1239,34 +1009,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>character_class_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>leader</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Wizard</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>character_class_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>warrior</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Warrior</t>
         </is>
       </c>
     </row>
@@ -1278,53 +1048,53 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>rogue</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Rogue</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>character_class_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>leader</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>Leader</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>character_class_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rogue</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rogue</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>adventure_length_choices</t>
+          <t>adventure_length_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1341,7 +1111,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>adventure_length_choices</t>
+          <t>adventure_length_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1358,7 +1128,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>adventure_length_choices</t>
+          <t>adventure_length_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1369,227 +1139,6 @@
       <c r="C17" t="inlineStr">
         <is>
           <t>Long</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adventure_type_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>adventure_story</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Adventure Story</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adventure_type_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>adventure_map</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Adventure Map</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>difficulty_level_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>difficulty_level_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>difficulty_level_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>character_class_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>wizard</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Wizard</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>character_class_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>character_class_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>rogue</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>character_class_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>wizard</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wizard</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>character_class_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>character_class_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>rogue</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Rogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>leader</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Leader</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>member</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Member</t>
         </is>
       </c>
     </row>
